--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -55,12 +55,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>BRAKE</t>
   </si>
   <si>
-    <t>중단</t>
+    <t>브레이크</t>
   </si>
   <si>
     <t>ENGINE</t>
@@ -72,64 +72,67 @@
     <t>Failed</t>
   </si>
   <si>
-    <t/>
+    <t>게임 실패</t>
   </si>
   <si>
     <t>GameOverUIForm.Back</t>
   </si>
   <si>
+    <t>뒤로</t>
+  </si>
+  <si>
     <t>Level.DisplayName1</t>
   </si>
   <si>
-    <t>관문 1 이름</t>
+    <t>레벨 1 이름</t>
   </si>
   <si>
     <t>Level.DisplayName2</t>
   </si>
   <si>
-    <t>관문 2 이름</t>
+    <t>레벨 2 이름</t>
   </si>
   <si>
     <t>Level.DisplayName3</t>
   </si>
   <si>
-    <t>관문 3 이름</t>
+    <t>레벨 3 이름</t>
   </si>
   <si>
     <t>Level.DisplayName4</t>
   </si>
   <si>
-    <t>관문 4 이름</t>
+    <t>레벨 4 이름</t>
   </si>
   <si>
     <t>Level.DisplayName5</t>
   </si>
   <si>
-    <t>관문 5 이름</t>
+    <t>레벨 5 이름</t>
   </si>
   <si>
     <t>MenuUIForm.Tips</t>
   </si>
   <si>
-    <t>시작 클릭</t>
+    <t>탭하여 시작</t>
   </si>
   <si>
     <t>Nothing</t>
   </si>
   <si>
-    <t>실현되지 않음</t>
+    <t>미구현</t>
   </si>
   <si>
     <t>OFF</t>
   </si>
   <si>
-    <t>끄기</t>
+    <t>꺼짐</t>
   </si>
   <si>
     <t>ON</t>
   </si>
   <si>
-    <t>켜기</t>
+    <t>켜짐</t>
   </si>
   <si>
     <t>RatingDialog.CancelTxt</t>
@@ -141,31 +144,43 @@
     <t>RatingDialog.Description</t>
   </si>
   <si>
-    <t>이 게임 좋아해요?\n 별 다섯 개 호평해 주세요!</t>
+    <t>이 게임이 마음에 드시나요?\n5점 별점을 부탁드립니다!</t>
   </si>
   <si>
     <t>RatingDialog.HighRatingTips</t>
   </si>
   <si>
-    <t>당신의 긍정에 감사 드립니다!우리는 더욱 분발할 것이다!</t>
+    <t>긍정적인 평가에 감사드립니다! 더욱 노력하겠습니다!</t>
   </si>
   <si>
     <t>RatingDialog.LowRatingTips</t>
   </si>
   <si>
-    <t>당신의 평가에 감사드립니다. 우리는 최선을 다해 최적화를 완비합니다!</t>
+    <t>평가해 주셔서 감사합니다, 더 나은 게임으로 발전하겠습니다!</t>
   </si>
   <si>
     <t>RatingDialog.RateTxt</t>
   </si>
   <si>
-    <t>별을 평가하다</t>
+    <t>별점</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>상점</t>
+  </si>
+  <si>
+    <t>STEERING</t>
+  </si>
+  <si>
+    <t>조종</t>
   </si>
   <si>
     <t>Settings.Help</t>
   </si>
   <si>
-    <t>도움말 / 피드백</t>
+    <t>도움말/피드백</t>
   </si>
   <si>
     <t>Settings.Language</t>
@@ -177,31 +192,31 @@
     <t>Settings.Music</t>
   </si>
   <si>
-    <t>배경음악</t>
+    <t>배경 음악</t>
   </si>
   <si>
     <t>Settings.Privacy</t>
   </si>
   <si>
-    <t>개인 정보 보호 프로토콜</t>
+    <t>개인정보 처리방침</t>
   </si>
   <si>
     <t>Settings.Rating</t>
   </si>
   <si>
-    <t>채점</t>
+    <t>평점</t>
   </si>
   <si>
     <t>Settings.SFX</t>
   </si>
   <si>
-    <t>음향 효과</t>
+    <t>효과음</t>
   </si>
   <si>
     <t>Settings.Title</t>
   </si>
   <si>
-    <t>설치</t>
+    <t>설정</t>
   </si>
   <si>
     <t>Settings.Vibrate</t>
@@ -210,15 +225,6 @@
     <t>진동</t>
   </si>
   <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>상점</t>
-  </si>
-  <si>
-    <t>STEERING</t>
-  </si>
-  <si>
     <t>TermsOfService</t>
   </si>
   <si>
@@ -232,6 +238,9 @@
   </si>
   <si>
     <t>Victory</t>
+  </si>
+  <si>
+    <t>게임 승리</t>
   </si>
 </sst>
 </file>
@@ -2153,6 +2162,130 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -4864,250 +4997,250 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5119,7 +5252,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId421" name="A1">
+            <control shapeId="1056" r:id="rId451" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5141,7 +5274,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId422" name="A2">
+            <control shapeId="1057" r:id="rId452" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5163,7 +5296,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId423" name="A3">
+            <control shapeId="1058" r:id="rId453" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5185,7 +5318,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId424" name="A4">
+            <control shapeId="1059" r:id="rId454" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5207,7 +5340,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId425" name="A5">
+            <control shapeId="1060" r:id="rId455" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5229,7 +5362,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId426" name="A6">
+            <control shapeId="1061" r:id="rId456" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5251,7 +5384,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId427" name="A7">
+            <control shapeId="1062" r:id="rId457" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5273,7 +5406,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId428" name="A8">
+            <control shapeId="1063" r:id="rId458" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5295,7 +5428,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId429" name="A9">
+            <control shapeId="1064" r:id="rId459" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5317,7 +5450,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId430" name="A10">
+            <control shapeId="1065" r:id="rId460" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5339,7 +5472,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId431" name="A11">
+            <control shapeId="1066" r:id="rId461" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5361,7 +5494,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId432" name="A12">
+            <control shapeId="1067" r:id="rId462" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5383,7 +5516,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId433" name="A13">
+            <control shapeId="1068" r:id="rId463" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5405,7 +5538,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId434" name="A14">
+            <control shapeId="1069" r:id="rId464" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5427,7 +5560,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId435" name="A15">
+            <control shapeId="1070" r:id="rId465" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5449,7 +5582,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId436" name="A16">
+            <control shapeId="1071" r:id="rId466" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5471,7 +5604,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId437" name="A17">
+            <control shapeId="1072" r:id="rId467" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5493,7 +5626,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId438" name="A18">
+            <control shapeId="1073" r:id="rId468" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5515,7 +5648,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId439" name="A19">
+            <control shapeId="1074" r:id="rId469" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5537,7 +5670,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId440" name="A20">
+            <control shapeId="1075" r:id="rId470" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5559,7 +5692,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId441" name="A21">
+            <control shapeId="1076" r:id="rId471" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5581,7 +5714,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId442" name="A22">
+            <control shapeId="1077" r:id="rId472" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5603,7 +5736,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId443" name="A23">
+            <control shapeId="1078" r:id="rId473" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5625,7 +5758,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId444" name="A24">
+            <control shapeId="1079" r:id="rId474" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5647,7 +5780,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId445" name="A25">
+            <control shapeId="1080" r:id="rId475" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5669,7 +5802,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId446" name="A26">
+            <control shapeId="1081" r:id="rId476" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5691,7 +5824,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId447" name="A27">
+            <control shapeId="1082" r:id="rId477" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5713,7 +5846,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId448" name="A28">
+            <control shapeId="1083" r:id="rId478" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5735,7 +5868,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId449" name="A29">
+            <control shapeId="1084" r:id="rId479" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5757,7 +5890,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId450" name="A30">
+            <control shapeId="1085" r:id="rId480" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5779,7 +5912,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId451" name="A31">
+            <control shapeId="1086" r:id="rId481" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
